--- a/excel/01认识Excel填充柄.xlsx
+++ b/excel/01认识Excel填充柄.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10914"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Desktop/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C549F9DE-7D96-024F-BDE2-26ABA2D81A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15DCA18-581F-AD4B-A268-C269ACDB742D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="神奇的填充柄" sheetId="16" r:id="rId3"/>
     <sheet name="智能填充柄2" sheetId="17" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="105">
   <si>
     <t>一、</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -400,6 +400,26 @@
   </si>
   <si>
     <t>自定义序列-文件-选项 mac版-上方Excel图标-偏好设置-自定义序列</t>
+  </si>
+  <si>
+    <t>Excel文件称为“工作簿”可由多张“工作表”组成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excel2010每张工作表由1048576行*16384列组成 行数也就是2的20次方</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格列标题使用数字显示 引用R1C1样式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单元格是组成表格的最小元素，在Excel中用“地址”来表示每一个单元格，并且可以通过使用这种“地址”来引用单元格中的数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Excel-偏好设置-计算-使用R1C1引用样式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5440,7 +5460,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor indexed="60"/>
   </sheetPr>
-  <dimension ref="A2:L62"/>
+  <dimension ref="A2:L68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -5527,214 +5547,249 @@
       </c>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C25" s="3" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="B26" s="9"/>
+      <c r="C26" s="27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="B27" s="9"/>
+    </row>
+    <row r="28" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C28" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="D26" s="26" t="s">
+    <row r="29" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="D29" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="L26" s="13"/>
-    </row>
-    <row r="27" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C27" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C28" s="9"/>
-      <c r="D28" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C29" s="9"/>
-      <c r="D29" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="L29" s="12"/>
+      <c r="L29" s="13"/>
     </row>
     <row r="30" spans="1:12" s="3" customFormat="1" ht="14">
       <c r="C30" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="3" customFormat="1">
+        <v>79</v>
+      </c>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" s="3" customFormat="1" ht="14">
       <c r="C31" s="9"/>
       <c r="D31" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C32" s="9"/>
+      <c r="D32" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="L32" s="12"/>
+    </row>
+    <row r="33" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C33" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="3" customFormat="1">
+      <c r="C34" s="9"/>
+      <c r="D34" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="G31" s="10"/>
-    </row>
-    <row r="32" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C32" s="9" t="s">
+      <c r="G34" s="10"/>
+    </row>
+    <row r="35" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C35" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C33" s="7" t="s">
+    <row r="36" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C36" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C34" s="7"/>
-      <c r="D34" s="28" t="s">
+    <row r="37" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C37" s="7"/>
+      <c r="D37" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="12"/>
-    </row>
-    <row r="35" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C35" s="7"/>
-      <c r="D35" s="28" t="s">
+      <c r="L37" s="12"/>
+    </row>
+    <row r="38" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C38" s="7"/>
+      <c r="D38" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="L35" s="12"/>
-    </row>
-    <row r="36" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="D36" s="28" t="s">
+      <c r="L38" s="12"/>
+    </row>
+    <row r="39" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="D39" s="28" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
-      <c r="A37" s="3"/>
-    </row>
-    <row r="38" spans="1:12" s="3" customFormat="1">
-      <c r="A38" s="1"/>
-    </row>
-    <row r="39" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="A39" s="3" t="s">
+    <row r="40" spans="1:12">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="3"/>
+      <c r="C41" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="3" customFormat="1">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="A45" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B45" s="8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B40" s="9" t="s">
+    <row r="46" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="B46" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C41" s="28" t="s">
+    <row r="47" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C47" s="28" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C42" s="28" t="s">
+    <row r="48" spans="1:12" s="3" customFormat="1" ht="14">
+      <c r="C48" s="28" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="3" customFormat="1" ht="14"/>
-    <row r="44" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B44" s="9" t="s">
+    <row r="49" spans="1:5" s="3" customFormat="1" ht="14"/>
+    <row r="50" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="B50" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B45" s="9"/>
-      <c r="C45" s="3" t="s">
+    <row r="51" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="B51" s="9"/>
+      <c r="C51" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B46" s="9"/>
-      <c r="D46" s="28" t="s">
+    <row r="52" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="B52" s="9"/>
+      <c r="D52" s="28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="B47" s="9"/>
-      <c r="D47" s="29" t="s">
+    <row r="53" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="B53" s="9"/>
+      <c r="D53" s="29" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="3" customFormat="1" ht="14">
-      <c r="C48" s="9"/>
-      <c r="D48" s="28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="3" customFormat="1" ht="14">
-      <c r="C49" s="9"/>
-      <c r="D49" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="3" customFormat="1" ht="14">
-      <c r="C50" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="27"/>
-    </row>
-    <row r="51" spans="1:5" s="3" customFormat="1" ht="14">
-      <c r="C51" s="9"/>
-      <c r="D51" s="28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="3" customFormat="1" ht="14">
-      <c r="C52" s="9"/>
-      <c r="D52" s="28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1">
-      <c r="C53" s="9"/>
-      <c r="D53" s="28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1">
+    <row r="54" spans="1:5" s="3" customFormat="1" ht="14">
       <c r="C54" s="9"/>
       <c r="D54" s="28" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="C55" s="9"/>
+      <c r="D55" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="C56" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="27"/>
+    </row>
+    <row r="57" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="C57" s="9"/>
+      <c r="D57" s="28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" s="3" customFormat="1" ht="14">
+      <c r="C58" s="9"/>
+      <c r="D58" s="28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1">
+      <c r="C59" s="9"/>
+      <c r="D59" s="28" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1">
+      <c r="C60" s="9"/>
+      <c r="D60" s="28" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="55" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1"/>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3" t="s">
+    <row r="61" spans="1:5" s="3" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3"/>
+      <c r="B62" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="3"/>
-      <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="B57" s="3"/>
-      <c r="C57" s="28" t="s">
+      <c r="C62" s="3"/>
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="B63" s="3"/>
+      <c r="C63" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="B59" s="3" t="s">
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="2:5">
+      <c r="B65" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="C60" s="28" t="s">
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="2:5">
+      <c r="C66" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="C61" s="28" t="s">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="2:5">
+      <c r="C67" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="B62" s="3"/>
-      <c r="E62" s="3"/>
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="2:5">
+      <c r="B68" s="3"/>
+      <c r="E68" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
